--- a/results/03_LDA_Classification/tables/mccv_confusion_matrix.xlsx
+++ b/results/03_LDA_Classification/tables/mccv_confusion_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -457,16 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>6835</v>
+        <v>8571</v>
       </c>
       <c r="D2" t="n">
-        <v>465</v>
-      </c>
-      <c r="E2" t="n">
-        <v>700</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3">
@@ -484,69 +476,42 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="C4" t="n">
-        <v>846</v>
+        <v>8571</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>154</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7681</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1465</v>
-      </c>
-      <c r="E5" t="n">
-        <v>854</v>
-      </c>
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Combined results from 1,000 CV iterations (test size: 20%)</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Combined results from 1,000 CV iterations (test size: 20%)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/03_LDA_Classification/tables/mccv_confusion_matrix.xlsx
+++ b/results/03_LDA_Classification/tables/mccv_confusion_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>Cluster C2</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -452,13 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>8571</v>
+        <v>155</v>
       </c>
       <c r="D2" t="n">
-        <v>429</v>
+        <v>213</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1632</v>
       </c>
     </row>
     <row r="3">
@@ -468,50 +476,77 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>1000</v>
+        <v>1705</v>
+      </c>
+      <c r="E3" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>Cluster C3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>76</v>
+      </c>
+      <c r="C4" t="n">
+        <v>804</v>
+      </c>
+      <c r="D4" t="n">
+        <v>625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>96</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8571</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>64</v>
+      </c>
+      <c r="C5" t="n">
+        <v>969</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2543</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6488</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Combined results from 1,000 CV iterations (test size: 20%)</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Combined results from 1,000 CV iterations (test size: 20%)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
